--- a/output/pdf_financials_xlsx/DOS.xlsx
+++ b/output/pdf_financials_xlsx/DOS.xlsx
@@ -2111,7 +2111,7 @@
         <v>0.000474</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.241706</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
@@ -2127,16 +2127,16 @@
         <v>0.376296</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000113</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.060844</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.055965</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.092237</v>
       </c>
     </row>
     <row r="35">
@@ -2227,7 +2227,7 @@
         <v>0.000474</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.241706</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
@@ -2243,16 +2243,16 @@
         <v>0.376296</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000113</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.060844</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.055965</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.092237</v>
       </c>
     </row>
     <row r="37">
@@ -2923,7 +2923,7 @@
         <v>0.000285</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.436226</v>
+        <v>0.19452</v>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
@@ -2942,13 +2942,13 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.38736</v>
+        <v>0.326516</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.058445</v>
+        <v>0.00248</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.242237</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="49">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
